--- a/data/Wohlen (AG)/investment_decision/Anglikon_MFH_until_2004_investment_decision.xlsx
+++ b/data/Wohlen (AG)/investment_decision/Anglikon_MFH_until_2004_investment_decision.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>70.3822876846011</v>
+        <v>29.08826405677805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>43833.6721054799</v>
       </c>
       <c r="F2" t="n">
-        <v>70.3822876846011</v>
+        <v>28.08699716275961</v>
       </c>
       <c r="G2" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="H2" t="n">
-        <v>70.38228768460112</v>
+        <v>30.09741510529738</v>
       </c>
       <c r="I2" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="J2" t="n">
-        <v>70.38228768460107</v>
+        <v>28.08699716275967</v>
       </c>
       <c r="K2" t="n">
         <v>43833.6721054799</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>93.79764833566998</v>
+        <v>47.9808993548062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>43833.6721054799</v>
       </c>
       <c r="F3" t="n">
-        <v>93.17115040823938</v>
+        <v>52.31133271297081</v>
       </c>
       <c r="G3" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="H3" t="n">
-        <v>94.16502766398762</v>
+        <v>49.34066006649876</v>
       </c>
       <c r="I3" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="J3" t="n">
-        <v>94.38565042596568</v>
+        <v>52.31133271297076</v>
       </c>
       <c r="K3" t="n">
         <v>43833.6721054799</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>124.0012382023366</v>
+        <v>154.6356398669965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>43833.6721054799</v>
       </c>
       <c r="F4" t="n">
-        <v>124.0012382023366</v>
+        <v>154.5298400227817</v>
       </c>
       <c r="G4" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="H4" t="n">
-        <v>127.9817980303884</v>
+        <v>153.5525793896871</v>
       </c>
       <c r="I4" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="J4" t="n">
-        <v>124.623269763334</v>
+        <v>154.5345346766014</v>
       </c>
       <c r="K4" t="n">
         <v>43833.6721054799</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>154.0549269129527</v>
+        <v>160.1797377028277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>43833.6721054799</v>
       </c>
       <c r="F5" t="n">
-        <v>152.8072689309693</v>
+        <v>158.340384205089</v>
       </c>
       <c r="G5" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="H5" t="n">
-        <v>152.9559299514785</v>
+        <v>160.0811929265505</v>
       </c>
       <c r="I5" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="J5" t="n">
-        <v>154.2333873457344</v>
+        <v>158.3266676347539</v>
       </c>
       <c r="K5" t="n">
         <v>43833.6721054799</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>154.0549269129526</v>
+        <v>160.1797377028277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>43833.6721054799</v>
       </c>
       <c r="F6" t="n">
-        <v>152.8072689309693</v>
+        <v>158.340384205089</v>
       </c>
       <c r="G6" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="H6" t="n">
-        <v>152.9559299514785</v>
+        <v>160.0811929265505</v>
       </c>
       <c r="I6" t="n">
         <v>43833.6721054799</v>
       </c>
       <c r="J6" t="n">
-        <v>154.2333873457344</v>
+        <v>158.3266676347539</v>
       </c>
       <c r="K6" t="n">
         <v>43833.6721054799</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>65.75050815821986</v>
+        <v>91.77570926966293</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>65.75050815821986</v>
+        <v>44.19256239031605</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>31.66070256607222</v>
+        <v>44.19256239031605</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>31.66070256607222</v>
+        <v>91.77570926966293</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>65.75050815821986</v>
+        <v>91.77570926966293</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>65.75050815821986</v>
+        <v>62.94300969600227</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>45.09401131795915</v>
+        <v>62.94300969600227</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>45.09401131795915</v>
+        <v>91.77570926966293</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>65.75050815821986</v>
+        <v>91.77570926966293</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>65.75050815821986</v>
+        <v>72.37998015777235</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>51.854902715838</v>
+        <v>72.37998015777235</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>51.854902715838</v>
+        <v>91.77570926966293</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>65.75050815821986</v>
+        <v>91.77570926966293</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>65.75050815821986</v>
+        <v>77.72310884311517</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>55.68285925261391</v>
+        <v>77.72310884311517</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>55.68285925261391</v>
+        <v>91.77570926966293</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>65.75050815821986</v>
+        <v>91.77570926966293</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>65.75050815821986</v>
+        <v>81.02088841729521</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>58.04547442085005</v>
+        <v>81.02088841729521</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>58.04547442085005</v>
+        <v>91.77570926966293</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01487784169244547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01481275790436555</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.0148516403975534</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01483047221744145</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01487784169244547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01481275790436555</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.0148516403975534</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01483047221744145</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01487784169244547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01481275790436555</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.0148516403975534</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01599013581176471</v>
+        <v>0.01483047221744145</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01665639147058823</v>
+        <v>0.01487784169244547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0166134874213452</v>
+        <v>0.01481275790436555</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01657247096840872</v>
+        <v>0.0148516403975534</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01665639147058823</v>
+        <v>0.01483047221744145</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01665639147058823</v>
+        <v>0.01487784169244547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0166134874213452</v>
+        <v>0.01481275790436555</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01657247096840872</v>
+        <v>0.0148516403975534</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01665639147058823</v>
+        <v>0.01483047221744145</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4641104949287222</v>
+        <v>0.7959503031074291</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4673574477558582</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="G17" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H17" t="n">
-        <v>0.462206476900116</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="I17" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4601381385065715</v>
+        <v>0.7888298276261918</v>
       </c>
       <c r="K17" t="n">
         <v>2.378532702</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4641104949287222</v>
+        <v>0.7959503031074291</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4673574477558582</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="G18" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H18" t="n">
-        <v>0.462206476900116</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="I18" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4601381385065715</v>
+        <v>0.7888298276261918</v>
       </c>
       <c r="K18" t="n">
         <v>2.378532702</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4641104949287222</v>
+        <v>0.7959503031074291</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4673574477558582</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="G19" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H19" t="n">
-        <v>0.462206476900116</v>
+        <v>0.7786863012499998</v>
       </c>
       <c r="I19" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4601381385065715</v>
+        <v>0.7888298276261918</v>
       </c>
       <c r="K19" t="n">
         <v>2.378532702</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1415793275000004</v>
+        <v>0.5663173099999999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1461378827320723</v>
+        <v>0.5616348339914672</v>
       </c>
       <c r="G20" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1504958808565734</v>
+        <v>0.5604071745933834</v>
       </c>
       <c r="I20" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1415793275000004</v>
+        <v>0.5663173099999999</v>
       </c>
       <c r="K20" t="n">
         <v>2.378532702</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1415793275000004</v>
+        <v>0.5663173099999999</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1461378827320723</v>
+        <v>0.5616348339914672</v>
       </c>
       <c r="G21" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1504958808565734</v>
+        <v>0.5604071745933834</v>
       </c>
       <c r="I21" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1415793275000004</v>
+        <v>0.5663173099999999</v>
       </c>
       <c r="K21" t="n">
         <v>2.378532702</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.02416148059081548</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.04159484820569337</v>
       </c>
       <c r="G28" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.0431340337028174</v>
       </c>
       <c r="I28" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.01030216868499429</v>
       </c>
       <c r="K28" t="n">
         <v>2.378532702</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.02416148059081548</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.04159484820569337</v>
       </c>
       <c r="G29" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0431340337028174</v>
       </c>
       <c r="I29" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.01030216868499429</v>
       </c>
       <c r="K29" t="n">
         <v>2.378532702</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.04739158642766823</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.05430673891115978</v>
       </c>
       <c r="G30" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.0501754740099515</v>
       </c>
       <c r="I30" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.05242459314684599</v>
       </c>
       <c r="K30" t="n">
         <v>2.378532702</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.07078966374999998</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>2.378532702</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.07078966374999998</v>
       </c>
       <c r="G31" t="n">
         <v>2.378532702</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.07078966374999998</v>
       </c>
       <c r="I31" t="n">
         <v>2.378532702</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.07078966374999998</v>
       </c>
       <c r="K31" t="n">
         <v>2.378532702</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>55.54204203913989</v>
+        <v>28.22234119641973</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>28.22234119641973</v>
+        <v>55.54204203913989</v>
       </c>
     </row>
     <row r="43">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>55.54204203913989</v>
+        <v>39.61348250560053</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>39.61348250560053</v>
+        <v>55.54204203913989</v>
       </c>
     </row>
     <row r="44">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>55.54204203913989</v>
+        <v>45.1331164869232</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>45.1331164869232</v>
+        <v>55.54204203913989</v>
       </c>
     </row>
     <row r="45">
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>55.54204203913989</v>
+        <v>48.1679657120551</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>48.1679657120551</v>
+        <v>55.54204203913989</v>
       </c>
     </row>
     <row r="46">
@@ -2137,10 +2137,10 @@
         <v>55.54204203913989</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>50.58987565246294</v>
       </c>
       <c r="G46" t="n">
-        <v>55.54204203913989</v>
+        <v>49.99803332144975</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>49.99803332144975</v>
+        <v>55.54204203913989</v>
       </c>
     </row>
     <row r="47">
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>2.515935338156278</v>
+        <v>2.347257491842918</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,22 +2359,22 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F52" t="n">
-        <v>2.761090251436828</v>
+        <v>2.773750000997355</v>
       </c>
       <c r="G52" t="n">
-        <v>12.0554534984351</v>
+        <v>2.65246991347948</v>
       </c>
       <c r="H52" t="n">
-        <v>2.765749051073147</v>
+        <v>2.348052198293627</v>
       </c>
       <c r="I52" t="n">
         <v>2.65246991347948</v>
       </c>
       <c r="J52" t="n">
-        <v>2.518591614732026</v>
+        <v>2.773750000997355</v>
       </c>
       <c r="K52" t="n">
-        <v>2.65246991347948</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="53">
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>2.515935338156278</v>
+        <v>2.347257491842918</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,22 +2396,22 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F53" t="n">
-        <v>2.761090251436828</v>
+        <v>2.773750000997355</v>
       </c>
       <c r="G53" t="n">
-        <v>12.0554534984351</v>
+        <v>4.319626515221984</v>
       </c>
       <c r="H53" t="n">
-        <v>2.765749051073147</v>
+        <v>2.348052198293627</v>
       </c>
       <c r="I53" t="n">
         <v>4.319626515221984</v>
       </c>
       <c r="J53" t="n">
-        <v>2.518591614732026</v>
+        <v>2.773750000997355</v>
       </c>
       <c r="K53" t="n">
-        <v>4.319626515221984</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="54">
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.816529970509022</v>
+        <v>2.651955948842149</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,22 +2433,22 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F54" t="n">
-        <v>3.085810521568316</v>
+        <v>3.047805229112963</v>
       </c>
       <c r="G54" t="n">
-        <v>12.0554534984351</v>
+        <v>5.436204311728474</v>
       </c>
       <c r="H54" t="n">
-        <v>3.067151647374324</v>
+        <v>2.654354781323097</v>
       </c>
       <c r="I54" t="n">
         <v>5.436204311728474</v>
       </c>
       <c r="J54" t="n">
-        <v>2.817276059362287</v>
+        <v>3.047619653953527</v>
       </c>
       <c r="K54" t="n">
-        <v>5.436204311728474</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="55">
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.97569329005267</v>
+        <v>3.047123411291528</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,22 +2470,22 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F55" t="n">
-        <v>2.950782252527851</v>
+        <v>2.930943780874224</v>
       </c>
       <c r="G55" t="n">
-        <v>12.0554534984351</v>
+        <v>6.223451707455931</v>
       </c>
       <c r="H55" t="n">
-        <v>2.950085403994214</v>
+        <v>3.047397896079969</v>
       </c>
       <c r="I55" t="n">
         <v>6.223451707455931</v>
       </c>
       <c r="J55" t="n">
-        <v>2.975862341993698</v>
+        <v>2.930718396874879</v>
       </c>
       <c r="K55" t="n">
-        <v>6.223451707455931</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="56">
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.97569329005267</v>
+        <v>3.047123411291528</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,22 +2507,22 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F56" t="n">
-        <v>2.950782252527851</v>
+        <v>2.930943780874224</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0554534984351</v>
+        <v>6.801688578681109</v>
       </c>
       <c r="H56" t="n">
-        <v>2.950085403994214</v>
+        <v>3.047397896079969</v>
       </c>
       <c r="I56" t="n">
         <v>6.801688578681109</v>
       </c>
       <c r="J56" t="n">
-        <v>2.975862341993698</v>
+        <v>2.930718396874879</v>
       </c>
       <c r="K56" t="n">
-        <v>6.801688578681109</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="57">
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0554534984351</v>
+        <v>2.65246991347948</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2.65246991347948</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="58">
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0554534984351</v>
+        <v>4.319626515221984</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>4.319626515221984</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="59">
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0554534984351</v>
+        <v>5.436204311728474</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>5.436204311728474</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="60">
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>12.0554534984351</v>
+        <v>6.223451707455931</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>6.223451707455931</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="61">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>12.0554534984351</v>
+        <v>6.801688578681109</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>6.801688578681109</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="62">
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.902632861847009</v>
+        <v>0.3917004723730788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F64" t="n">
-        <v>1.933392296162377</v>
+        <v>0.4626459985415404</v>
       </c>
       <c r="G64" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="H64" t="n">
-        <v>1.933392296162376</v>
+        <v>0.4122888915228486</v>
       </c>
       <c r="I64" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="J64" t="n">
-        <v>1.901627276627317</v>
+        <v>0.4627889237037249</v>
       </c>
       <c r="K64" t="n">
         <v>12.0554534984351</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.902632861847009</v>
+        <v>0.4119996184206307</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F65" t="n">
-        <v>1.933392296162377</v>
+        <v>0.5448894099354189</v>
       </c>
       <c r="G65" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="H65" t="n">
-        <v>1.933392296162376</v>
+        <v>0.4126203933465026</v>
       </c>
       <c r="I65" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="J65" t="n">
-        <v>1.901627276627317</v>
+        <v>0.5452394062511516</v>
       </c>
       <c r="K65" t="n">
         <v>12.0554534984351</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.902632861847009</v>
+        <v>0.4119996184206307</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>12.0554534984351</v>
       </c>
       <c r="F66" t="n">
-        <v>1.933392296162377</v>
+        <v>0.5448894099354189</v>
       </c>
       <c r="G66" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="H66" t="n">
-        <v>1.933392296162376</v>
+        <v>0.4126203933465026</v>
       </c>
       <c r="I66" t="n">
         <v>12.0554534984351</v>
       </c>
       <c r="J66" t="n">
-        <v>1.901627276627317</v>
+        <v>0.5452394062511516</v>
       </c>
       <c r="K66" t="n">
         <v>12.0554534984351</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7380747797777883</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7380747797777883</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1.316598948647958</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.316598948647958</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1.787962369433086</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.787962369433086</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2.183030051402989</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2.183030051402989</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2.520626068883493</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2.520626068883493</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3000399853746616</v>
+        <v>0.4658336358741327</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>12.0554534984351</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.452685773505137</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7380747797777883</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2973837087989138</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7380747797777883</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3000399853746616</v>
+        <v>0.4658336358741327</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         <v>12.0554534984351</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.452685773505137</v>
       </c>
       <c r="I78" t="n">
-        <v>1.316598948647958</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2973837087989138</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>1.316598948647958</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3000399853746616</v>
+        <v>0.4658336358741327</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3364,16 +3364,16 @@
         <v>12.0554534984351</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.452685773505137</v>
       </c>
       <c r="I79" t="n">
-        <v>1.787962369433086</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2973837087989138</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1.787962369433086</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>2.183030051402989</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>2.183030051402989</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2.520626068883493</v>
+        <v>12.0554534984351</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2.520626068883493</v>
+        <v>12.0554534984351</v>
       </c>
     </row>
     <row r="82">
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3960,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
